--- a/Procurement/_документы/Дополнение № 1 в план закупок – IV кв. 2026.xlsx
+++ b/Procurement/_документы/Дополнение № 1 в план закупок – IV кв. 2026.xlsx
@@ -105,9 +105,6 @@
     <t>Дополнение № 1 в План закупок товаров, работ и неконсультационных услуг ЦАКФ на IV квартал 2026 года</t>
   </si>
   <si>
-    <t>Проект от 19.10.2026. Дополнительные позиции к Плану закупок на IV квартал 2026 года (нумерация продолжает план – позиции 81–83). Цены – с НДС по сайтам поставщиков в Астане (ссылки – лист «Ссылки на примеры»); жалюзи – ориентировочно, площадь и цена уточняются после бесплатного замера.</t>
-  </si>
-  <si>
     <t>Стул офисный для посетителей</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>Вертикальные тканевые жалюзи на окна зоны 710 (кабинеты 3, 4, 6 и open space 5): алюминиевый карниз, ламели 89 мм, нейтральный цвет (серый/бежевый), управление цепочкой; замер, изготовление и монтаж – в цене. Объём – ориентировочно 50 м² (≈20 м остекления по фасаду × ≈2,5 м), уточняется замером.</t>
   </si>
   <si>
-    <t>Оснащение; ед. – м²; ориентир 4 000–4 500 ₸/м² (basar-premium.kz, roll-dezign.kz) + запас на ткань и монтаж</t>
-  </si>
-  <si>
     <t>Декоративное растение напольное в высоком кашпо</t>
   </si>
   <si>
@@ -253,6 +247,12 @@
   </si>
   <si>
     <t>вариант подороже</t>
+  </si>
+  <si>
+    <t>Проект от 20.10.2026. Дополнительные позиции к Плану закупок на IV квартал 2026 года (нумерация продолжает план – позиции 81–83). Цены – с НДС по сайтам поставщиков в Астане (ссылки – лист «Ссылки на примеры»); жалюзи – ориентировочно, площадь и цена уточняются после бесплатного замера.</t>
+  </si>
+  <si>
+    <t>Оснащение; 1 комплект на окна зоны 710 с установкой, сумма 428 736 ₸ с НДС 16% (по расчёту поставщика)</t>
   </si>
 </sst>
 </file>
@@ -394,6 +394,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -402,11 +407,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -761,21 +761,21 @@
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -795,21 +795,21 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -829,21 +829,21 @@
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="A8" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
     </row>
     <row r="9" spans="1:13" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -938,13 +938,13 @@
         <v>17</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="G11" s="5">
         <v>15</v>
@@ -963,10 +963,10 @@
         <v>20</v>
       </c>
       <c r="L11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -977,26 +977,26 @@
         <v>82</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="5">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H12" s="5">
-        <v>5500</v>
+        <v>428736</v>
       </c>
       <c r="I12" s="5">
         <f>ROUND(G12*H12,0)</f>
-        <v>275000</v>
+        <v>428736</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>19</v>
@@ -1005,10 +1005,10 @@
         <v>20</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -1022,10 +1022,10 @@
         <v>17</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>21</v>
@@ -1047,10 +1047,10 @@
         <v>20</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -1058,7 +1058,7 @@
       <c r="B14" s="8"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8"/>
@@ -1066,7 +1066,7 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6">
         <f>SUM(I11:I13)</f>
-        <v>538478</v>
+        <v>692214</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -1097,25 +1097,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="C3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="E3" s="10" t="s">
         <v>42</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -1123,16 +1123,16 @@
         <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -1140,16 +1140,16 @@
         <v>81</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1157,16 +1157,16 @@
         <v>81</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -1174,16 +1174,16 @@
         <v>82</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1191,16 +1191,16 @@
         <v>82</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -1208,16 +1208,16 @@
         <v>83</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -1225,16 +1225,16 @@
         <v>83</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1242,16 +1242,16 @@
         <v>83</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
